--- a/data/Production_Reminders.xlsx
+++ b/data/Production_Reminders.xlsx
@@ -431,15 +431,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,489 +467,409 @@
           <t>Role</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U001</t>
+          <t>USR-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ravi Kumar</t>
+          <t>Alice Accountant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ravi.k@example.com</t>
+          <t>alice@example.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+919876543210</t>
+          <t>+1234567890</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>Accountant</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>USR-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Sharma</t>
+          <t>Bob Bookkeeper</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>priya.s@example.com</t>
+          <t>bob@example.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+919876543211</t>
+          <t>+1987654321</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>Accountant</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>USR-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amit Patel</t>
+          <t>Charlie CFO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>amit.p@example.com</t>
+          <t>charlie@example.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+919876543212</t>
+          <t>+1122334455</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Accountant</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>Finance Manager</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>USR-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sneha Reddy</t>
+          <t>Diana Director</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sneha.r@example.com</t>
+          <t>diana@example.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+919876543213</t>
+          <t>+1555666777</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Accountant</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>Finance Manager</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U005</t>
+          <t>USR-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Eve Executive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vikram.s@example.com</t>
+          <t>eve@example.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+919876543214</t>
+          <t>+1999888777</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Accountant</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>HR Executive</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U006</t>
+          <t>USR-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anjali Desai</t>
+          <t>Frank HR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anjali.d@example.com</t>
+          <t>frank@example.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+919876543215</t>
+          <t>+1444333222</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>HR Executive</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>HR</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U007</t>
+          <t>USR-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>Grace Auditor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rahul.v@example.com</t>
+          <t>grace@example.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+919876543216</t>
+          <t>+1777888999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HR Executive</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HR</t>
+          <t>Auditor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U008</t>
+          <t>USR-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kavita Iyer</t>
+          <t>Hank Helper</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kavita.i@example.com</t>
+          <t>hank@example.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+919876543217</t>
+          <t>+1333222111</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>Accountant</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U009</t>
+          <t>USR-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Manoj Tiwari</t>
+          <t>Ivy Inspector</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manoj.t@example.com</t>
+          <t>ivy@example.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+919876543218</t>
+          <t>+1666555444</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Auditor</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Audit</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U010</t>
+          <t>USR-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pooja Joshi</t>
+          <t>Jack Junior</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pooja.j@example.com</t>
+          <t>jack@example.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>+919876543219</t>
+          <t>+1222111000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Auditor</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Audit</t>
+          <t>Accountant</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U011</t>
+          <t>USR-011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sanjay Gupta</t>
+          <t>Karen Keys</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sanjay.g@example.com</t>
+          <t>karen@example.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+919876543220</t>
+          <t>+1888777666</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Accountant</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Finance</t>
+          <t>Finance Manager</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>USR-012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Neha Malhotra</t>
+          <t>Leo Ledger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>neha.m@example.com</t>
+          <t>leo@example.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+919876543221</t>
+          <t>+1000999888</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Accountant</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U013</t>
+          <t>USR-013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Karthik Nair</t>
+          <t>Mona Money</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>karthik.n@example.com</t>
+          <t>mona@example.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+919876543222</t>
+          <t>+1111222333</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Finance Manager</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U014</t>
+          <t>USR-014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Simran Kaur</t>
+          <t>Nina Numbers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>simran.k@example.com</t>
+          <t>nina@example.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+919876543223</t>
+          <t>+1444555666</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HR Executive</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>HR</t>
+          <t>Auditor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U015</t>
+          <t>USR-015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arun Jha</t>
+          <t>Oscar Officer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>arun.j@example.com</t>
+          <t>oscar@example.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+919876543224</t>
+          <t>+1777666555</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auditor</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Audit</t>
+          <t>Compliance Officer</t>
         </is>
       </c>
     </row>
@@ -965,13 +884,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -990,16 +908,11 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Owner_ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>MOD-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1009,19 +922,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Goods and Services Tax filings</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>U002</t>
+          <t>Goods and Services Tax filings and reconciliations.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>MOD-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1031,19 +939,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salary processing and compliance</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>U006</t>
+          <t>Salary, PF, ESIC, and PT processing.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>MOD-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1053,19 +956,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tax Deducted at Source submissions</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>U008</t>
+          <t>Tax Deducted at Source payments and returns.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>MOD-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1075,19 +973,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Accounts Payable processing</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>U013</t>
+          <t>Accounts Payable and vendor reconciliations.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>MOD-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1097,19 +990,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Statutory compliance and filings</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>U001</t>
+          <t>Statutory and regulatory compliance.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>MOD-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1119,19 +1007,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Internal and external audits</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>U009</t>
+          <t>Internal and external audit preparations.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>MOD-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1141,12 +1024,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIS and Financial statements</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>U002</t>
+          <t>MIS, P&amp;L, Balance Sheet preparations.</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1043,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1191,52 +1069,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Module_ID</t>
+          <t>Frequency</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Assignee_ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Email_Enabled</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WhatsApp_Enabled</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Email_Enabled</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>WhatsApp_Enabled</t>
-        </is>
-      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Remark</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Link</t>
         </is>
       </c>
     </row>
@@ -1253,52 +1131,52 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>USR-001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>GST portal filing.</t>
+          <t>https://gst.gov.in</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>File outward supplies</t>
         </is>
       </c>
     </row>
@@ -1315,52 +1193,52 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>USR-001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GST portal filing.</t>
+          <t>https://gst.gov.in</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Monthly return and payment</t>
         </is>
       </c>
     </row>
@@ -1372,57 +1250,53 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GSTR-9 Annual Return</t>
+          <t>GSTR-2B Reconciliation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>USR-008</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Annual reconciliation.</t>
-        </is>
-      </c>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Reconcile ITC</t>
         </is>
       </c>
     </row>
@@ -1434,57 +1308,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GST Recon with 2A/2B</t>
+          <t>GSTR-9 Annual Return</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>U013</t>
+          <t>December</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>USR-003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Reconciliation.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Annual return filing</t>
         </is>
       </c>
     </row>
@@ -1496,57 +1366,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GST Payment</t>
+          <t>GSTR-9C Reconciliation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M01</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>U005</t>
+          <t>December</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>USR-007</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Tax payment to government.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Audit certification</t>
         </is>
       </c>
     </row>
@@ -1558,57 +1424,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salary Processing</t>
+          <t>LUT Renewal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>U006</t>
+          <t>March</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Last Day</t>
+          <t>USR-015</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Process bank transfers.</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Letter of Undertaking for exports</t>
         </is>
       </c>
     </row>
@@ -1620,57 +1482,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PF Payment</t>
+          <t>E-Way Bill Reconciliation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>U014</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>USR-012</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Provident fund remittance.</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Check e-way bills generated vs sales</t>
         </is>
       </c>
     </row>
@@ -1682,57 +1540,57 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESIC Payment</t>
+          <t>Salary Processing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>U014</t>
+          <t>Last Day</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>USR-005</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Employee State Insurance.</t>
+          <t>https://hr.system.com</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Finalize attendance and process salaries</t>
         </is>
       </c>
     </row>
@@ -1744,57 +1602,57 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Payment</t>
+          <t>PF Payment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>U014</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>USR-006</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Professional Tax.</t>
+          <t>https://epfindia.gov.in</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Provident Fund deposit</t>
         </is>
       </c>
     </row>
@@ -1806,57 +1664,57 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Issue Payslips</t>
+          <t>ESIC Payment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>U014</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>USR-006</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Distribute to employees.</t>
+          <t>https://esic.in</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>ESIC deposit</t>
         </is>
       </c>
     </row>
@@ -1868,57 +1726,53 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quarterly TDS Return (Form 24Q)</t>
+          <t>Professional Tax (PT) Payment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M02</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>U006</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>USR-005</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Payroll TDS.</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>State-specific PT</t>
         </is>
       </c>
     </row>
@@ -1930,57 +1784,53 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TDS Payment (Non-Salary)</t>
+          <t>TDS on Salary Payment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>USR-005</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Deposit to bank.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Deposit TDS deducted from salaries</t>
         </is>
       </c>
     </row>
@@ -1992,57 +1842,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quarterly TDS Return (Form 26Q)</t>
+          <t>Quarterly PF Return</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>U005</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>USR-006</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Non-salary TDS return.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>File PF returns</t>
         </is>
       </c>
     </row>
@@ -2054,57 +1900,53 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Issue Form 16/16A</t>
+          <t>Annual Appraisals Review</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>April</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>USR-003</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Issue to vendors/employees.</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Finalize increments</t>
         </is>
       </c>
     </row>
@@ -2116,57 +1958,57 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TDS Reconciliation</t>
+          <t>TDS Payment (Non-Salary)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>TDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>USR-002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Reconcile with books.</t>
+          <t>https://incometax.gov.in</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Deposit TDS for contractors/rent/professionals</t>
         </is>
       </c>
     </row>
@@ -2178,57 +2020,53 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Collect Lower Deduction Certs</t>
+          <t>Form 26Q Filing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M03</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>TDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>USR-002</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>From vendors.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>TDS return for non-salary</t>
         </is>
       </c>
     </row>
@@ -2240,57 +2078,53 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vendor Payment Run (A-M)</t>
+          <t>Form 24Q Filing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>U011</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>TDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>USR-005</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Clear approved invoices.</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>TDS return for salary</t>
         </is>
       </c>
     </row>
@@ -2302,57 +2136,53 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vendor Payment Run (N-Z)</t>
+          <t>Form 27Q Filing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>U005</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bi-Weekly</t>
+          <t>TDS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>USR-002</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Clear approved invoices.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>TDS return for NRI</t>
         </is>
       </c>
     </row>
@@ -2364,57 +2194,53 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Urgent Vendor Payments</t>
+          <t>Issue TDS Certificates (Form 16A)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>TDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>USR-010</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Ad-hoc urgent clearing.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Distribute certificates to vendors</t>
         </is>
       </c>
     </row>
@@ -2426,57 +2252,53 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vendor Ageing Report</t>
+          <t>Issue Form 16 (Salary)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>June</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>TDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>USR-006</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Review payables.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Distribute Form 16 to employees</t>
         </is>
       </c>
     </row>
@@ -2488,57 +2310,57 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reconcile Vendor SOA</t>
+          <t>Vendor Payment Run</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M04</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>U008</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Vendor Payments</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>USR-004</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Statement of accounts.</t>
+          <t>https://erp/ap</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Process approved vendor invoices</t>
         </is>
       </c>
     </row>
@@ -2550,57 +2372,53 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Income Tax Filing (Company)</t>
+          <t>Vendor Ledger Reconciliation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Vendor Payments</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>USR-012</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>ITR-6 Filing.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Reconcile major vendors</t>
         </is>
       </c>
     </row>
@@ -2612,57 +2430,53 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Advance Tax Payment (Q1)</t>
+          <t>MSME Payment Review</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Vendor Payments</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>USR-011</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>15th June.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Ensure MSME payments within 45 days</t>
         </is>
       </c>
     </row>
@@ -2674,57 +2488,53 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Advance Tax Payment (Q2)</t>
+          <t>Expense Reimbursement Run</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>U005</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Vendor Payments</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>USR-008</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>15th September.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Clear employee expenses</t>
         </is>
       </c>
     </row>
@@ -2736,57 +2546,57 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Advance Tax Payment (Q3)</t>
+          <t>Income Tax Advance Tax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>U005</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>USR-003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>15th December.</t>
+          <t>https://incometax.gov.in</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Pay advance income tax installments</t>
         </is>
       </c>
     </row>
@@ -2798,57 +2608,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Advance Tax Payment (Q4)</t>
+          <t>Income Tax Filing (Company)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>October</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>USR-003</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>15th March.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Annual ITR filing</t>
         </is>
       </c>
     </row>
@@ -2860,57 +2666,57 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MCA Annual Return (AOC-4)</t>
+          <t>ROC Annual Return (MGT-7)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>U013</t>
+          <t>November</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>USR-015</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>RoC Filing.</t>
+          <t>https://mca.gov.in</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>File ROC returns</t>
         </is>
       </c>
     </row>
@@ -2922,57 +2728,53 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MCA Annual Return (MGT-7)</t>
+          <t>Financial Statements (AOC-4)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>October</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>USR-015</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>RoC Filing.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>File financials with ROC</t>
         </is>
       </c>
     </row>
@@ -2984,57 +2786,53 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Director KYC (DIR-3)</t>
+          <t>Secretarial Audit Report</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>September</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>USR-015</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>MCA Portal.</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Prepare secretarial audit</t>
         </is>
       </c>
     </row>
@@ -3046,57 +2844,53 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trade License Renewal</t>
+          <t>FEMA Compliance (FLA Return)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M05</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>July</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>USR-004</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Local municipality.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Foreign Liabilities and Assets return</t>
         </is>
       </c>
     </row>
@@ -3108,57 +2902,53 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quarterly Internal Audit</t>
+          <t>Board Meeting Preparation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>U010</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>USR-013</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Internal checks.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Draft agenda and minutes</t>
         </is>
       </c>
     </row>
@@ -3175,52 +2965,48 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>U015</t>
+          <t>May</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>USR-007</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Prepare schedules.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Prepare schedules for statutory auditors</t>
         </is>
       </c>
     </row>
@@ -3237,52 +3023,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>U010</t>
+          <t>August</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>USR-009</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Form 3CD prep.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Prepare Form 3CD schedules</t>
         </is>
       </c>
     </row>
@@ -3294,57 +3076,53 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Inventory Physical Verification</t>
+          <t>Internal Audit (Q1)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>U015</t>
+          <t>July</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>USR-014</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Count stock.</t>
-        </is>
-      </c>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Conduct Q1 internal audit</t>
         </is>
       </c>
     </row>
@@ -3356,57 +3134,53 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fixed Asset Verification</t>
+          <t>Internal Audit (Q2)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>U015</t>
+          <t>October</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>USR-014</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Tagging and count.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Conduct Q2 internal audit</t>
         </is>
       </c>
     </row>
@@ -3418,57 +3192,53 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Review Audit Findings</t>
+          <t>Internal Audit (Q3)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M06</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>U015</t>
+          <t>January</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>USR-014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Management review.</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Conduct Q3 internal audit</t>
         </is>
       </c>
     </row>
@@ -3480,53 +3250,53 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daily Bank Reconciliation</t>
+          <t>Internal Audit (Q4)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>April</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>Audits</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>USR-014</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Match bank lines.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Conduct Q4 internal audit</t>
         </is>
       </c>
     </row>
@@ -3538,53 +3308,53 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Daily Cash Flow Report</t>
+          <t>Inventory Verification</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>March</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>Audits</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>USR-009</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Morning cash position.</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Physical stock verification</t>
         </is>
       </c>
     </row>
@@ -3596,57 +3366,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Weekly Sales Report</t>
+          <t>Daily Bank Reconciliation</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>M07</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>U013</t>
-        </is>
-      </c>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>USR-010</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Sales review.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Match daily bank statements</t>
         </is>
       </c>
     </row>
@@ -3658,57 +3420,53 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Weekly Collections Report</t>
+          <t>Monthly MIS Report</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>USR-011</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>AR Review.</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Publish monthly financials to management</t>
         </is>
       </c>
     </row>
@@ -3720,57 +3478,53 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Monthly MIS Preparation</t>
+          <t>Cash Flow Forecast</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>USR-004</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Profit &amp; Loss, Balance Sheet.</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Update 13-week cash flow</t>
         </is>
       </c>
     </row>
@@ -3782,57 +3536,53 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Monthly Board Pack</t>
+          <t>Debtors Ageing Review</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>U003</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>USR-001</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Deck for directors.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Follow up on overdue invoices</t>
         </is>
       </c>
     </row>
@@ -3844,57 +3594,53 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Budget vs Actuals Review</t>
+          <t>Fixed Asset Register Update</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>U012</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>USR-012</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Variance analysis.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Capitalize new assets and run depreciation</t>
         </is>
       </c>
     </row>
@@ -3911,52 +3657,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>USR-008</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Match group books.</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Match balances with subsidiary</t>
         </is>
       </c>
     </row>
@@ -3968,57 +3710,53 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Update Rolling Forecast</t>
+          <t>Budget vs Actuals Variance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Financial Reports</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>USR-013</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Financial projection.</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Analyze departmental variances</t>
         </is>
       </c>
     </row>
@@ -4030,57 +3768,53 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Month-End Provisions</t>
+          <t>Backup Financial Data</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>U002</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>USR-003</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Accruals entry.</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Ensure ERP backups are secure</t>
         </is>
       </c>
     </row>
@@ -4092,57 +3826,53 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Depreciation Run</t>
+          <t>Review Software Subscriptions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Vendor Payments</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>USR-011</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>ERP automated run.</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Cancel unused SaaS tools</t>
         </is>
       </c>
     </row>
@@ -4154,57 +3884,53 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Review Suspense Accounts</t>
+          <t>GST Clarification Replies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>U011</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>USR-001</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Clear pending entries.</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Check portal for notices</t>
         </is>
       </c>
     </row>
@@ -4216,57 +3942,53 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Credit Card Reconciliation</t>
+          <t>Employee Expense Audit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>U008</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Audits</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>USR-007</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Corporate cards.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Sample check travel expenses</t>
         </is>
       </c>
     </row>
@@ -4278,73 +4000,69 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Petty Cash Replenishment</t>
+          <t>Insurance Policy Renewal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>Yearly</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>U004</t>
+          <t>March</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>USR-015</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Physical cash count.</t>
-        </is>
-      </c>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>https://erp.hitech.local</t>
+          <t>Renew D&amp;O and Fire policies</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C2:C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Daily,Weekly,Bi-Weekly,Monthly,Quarterly,Yearly"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pending,In Progress,Completed,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:J100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="G2:H100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Critical,High,Medium,Low"</formula1>
+    <dataValidation sqref="I2:I100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4361,7 +4079,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4403,24 +4121,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Timezone</t>
+          <t>Retry_Interval_Hours</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Asia/Kolkata</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Company_Name</t>
+          <t>Timezone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HITECH Industries</t>
+          <t>Asia/Kolkata</t>
         </is>
       </c>
     </row>
@@ -4435,11 +4153,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4486,19 +4204,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>reminders@hitech.local</t>
+          <t>finance-reminders@hitech.local</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Daily_Digest</t>
+          <t>Enable_SSL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CC_Management</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cfo@example.com</t>
         </is>
       </c>
     </row>
@@ -4513,11 +4243,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4540,7 +4270,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>daily_activity_reminder</t>
+          <t>finance_task_reminder_v1</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4289,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API_Version</t>
+          <t>Phone_Number_ID</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>v20.0</t>
+          <t>101234567890123</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Business_Account_ID</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>109876543210987</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4587,7 +4329,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4625,16 +4367,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RUN-8000</t>
+          <t>RUN-9001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4651,16 +4393,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RUN-8001</t>
+          <t>RUN-9002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4669,32 +4411,28 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RUN-8002</t>
+          <t>RUN-9003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Sent</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4702,25 +4440,21 @@
           <t>Sent</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RUN-8003</t>
+          <t>RUN-9004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4737,16 +4471,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RUN-8004</t>
+          <t>RUN-9005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4755,28 +4489,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Timeout</t>
-        </is>
-      </c>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RUN-8005</t>
+          <t>RUN-9006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4793,16 +4523,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RUN-8006</t>
+          <t>RUN-9007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4819,16 +4549,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RUN-8007</t>
+          <t>RUN-9008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4845,16 +4575,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RUN-8008</t>
+          <t>RUN-9009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4871,132 +4601,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUN-8009</t>
+          <t>RUN-9010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Sent</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RUN-8010</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RUN-8011</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RUN-8012</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RUN-8013</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SMTP Timeout.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5009,7 +4639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5017,6 +4647,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5045,16 +4676,21 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>User_ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMP-1000</t>
+          <t>IMP-2001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-05 15:47:53</t>
+          <t>2026-07-16 14:01:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5064,24 +4700,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Success</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>USR-003</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IMP-1001</t>
+          <t>IMP-2002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 17:47:53</t>
+          <t>2026-07-17 21:01:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5091,24 +4732,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Success</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>USR-001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMP-1002</t>
+          <t>IMP-2003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07 17:47:53</t>
+          <t>2026-07-18 22:01:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5118,24 +4764,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Success</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>USR-001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMP-1003</t>
+          <t>IMP-2004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08 12:47:53</t>
+          <t>2026-07-19 15:01:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5145,24 +4796,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Success</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>USR-003</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMP-1004</t>
+          <t>IMP-2005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-09 14:47:53</t>
+          <t>2026-07-20 17:01:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5172,7 +4828,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5180,139 +4836,9 @@
           <t>Success</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>IMP-1005</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-10 13:47:53</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>IMP-1006</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-11 20:47:53</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>IMP-1007</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-07-12 15:47:53</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IMP-1008</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-13 13:47:53</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>IMP-1009</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-07-14 20:47:53</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Success</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>USR-003</t>
         </is>
       </c>
     </row>
